--- a/event_planner_forms/001_graduation_ceremony_rsvp_form--event_planner_forms.xlsx
+++ b/event_planner_forms/001_graduation_ceremony_rsvp_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>graduation_date</t>
+          <t>graduation_date_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Graduation Date</t>
+          <t>Graduation Date 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Graduation Ceremony Rsvp Form Comments</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>graduation_ceremony_rsvp_form_signature</t>
+          <t>graduation_ceremony_rsvp_form_signature_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Graduation Ceremony Rsvp Form Signature 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>graduation_ceremony_rsvp_form_signature</t>
+          <t>graduation_ceremony_rsvp_form_signature_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Graduation Ceremony Rsvp Form Signature 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1263,8 +1263,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'graduation'}</t>
+          <t>graduation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Graduation'}</t>
+          <t>Graduation</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'commencement'}</t>
+          <t>commencement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Commencement'}</t>
+          <t>Commencement</t>
         </is>
       </c>
     </row>
